--- a/artfynd/A 17953-2025 artfynd.xlsx
+++ b/artfynd/A 17953-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124824995</v>
+        <v>124824969</v>
       </c>
       <c r="B2" t="n">
         <v>57666</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 17953-2025 artfynd.xlsx
+++ b/artfynd/A 17953-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124824969</v>
+        <v>124824995</v>
       </c>
       <c r="B2" t="n">
         <v>57666</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 17953-2025 artfynd.xlsx
+++ b/artfynd/A 17953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124824995</v>
+        <v>124824969</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 17953-2025 artfynd.xlsx
+++ b/artfynd/A 17953-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Moritz Moser, Sven Halling</t>
+          <t>Sven Halling, Moritz Moser, Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 17953-2025 artfynd.xlsx
+++ b/artfynd/A 17953-2025 artfynd.xlsx
@@ -680,11 +680,6 @@
       <c r="B2" t="n">
         <v>57793</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>NT</t>
@@ -785,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sven Halling, Moritz Moser, Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Moritz Moser, Sven Halling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
